--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_dl_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_dl_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>17-06-2021 08:30</t>
+          <t>2021-06-17 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -814,7 +814,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -909,7 +909,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>17-08-2021 08:30</t>
+          <t>2021-08-17 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>11-12-2021 08:30</t>
+          <t>2021-11-12 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>23-06-2021 08:30</t>
+          <t>2021-06-23 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>23-06-2021 08:30</t>
+          <t>2021-06-23 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>26-11-2021 08:30</t>
+          <t>2021-11-26 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>30-11-2021 08:30</t>
+          <t>2021-11-30 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>26-11-2021 08:30</t>
+          <t>2021-11-26 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>26-11-2021 08:30</t>
+          <t>2021-11-26 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>12-12-2021 08:30</t>
+          <t>2021-12-12 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>20-12-2021 08:30</t>
+          <t>2021-12-20 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>30-11-2021 08:30</t>
+          <t>2021-11-30 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>26-11-2021 08:30</t>
+          <t>2021-11-26 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>17-12-2021 08:30</t>
+          <t>2021-12-17 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>25-11-2021 08:30</t>
+          <t>2021-11-25 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>20-12-2021 08:30</t>
+          <t>2021-12-20 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>25-11-2021 08:30</t>
+          <t>2021-11-25 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>20-12-2021 08:30</t>
+          <t>2021-12-20 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>25-11-2021 08:30</t>
+          <t>2021-11-25 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>17-12-2021 08:30</t>
+          <t>2021-12-17 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>25-11-2021 08:30</t>
+          <t>2021-11-25 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>25-11-2021 08:30</t>
+          <t>2021-11-25 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>25-11-2021 08:30</t>
+          <t>2021-11-25 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>30-11-2021 08:30</t>
+          <t>2021-11-30 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>17-12-2021 08:30</t>
+          <t>2021-12-17 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>25-11-2021 08:30</t>
+          <t>2021-11-25 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>25-11-2021 08:30</t>
+          <t>2021-11-25 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>26-11-2021 08:30</t>
+          <t>2021-11-26 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>30-11-2021 08:30</t>
+          <t>2021-11-30 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>20-12-2021 08:30</t>
+          <t>2021-12-20 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>17-12-2021 08:30</t>
+          <t>2021-12-17 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>20-12-2021 08:30</t>
+          <t>2021-12-20 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>17-12-2021 08:30</t>
+          <t>2021-12-17 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>30-11-2021 08:30</t>
+          <t>2021-11-30 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>30-11-2021 08:30</t>
+          <t>2021-11-30 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="n">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="n">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="inlineStr"/>
